--- a/Экономика/Лабораторная работа 4_ФОТ_с.xlsx
+++ b/Экономика/Лабораторная работа 4_ФОТ_с.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Labs_6\Экономика\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F8950F-E6F2-4BE5-9FAC-1D60471D496D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4754D83D-1288-4DF8-A01F-BBD7AFE44887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1213,48 +1213,48 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1557,36 +1557,36 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="94"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="89"/>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="87" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="89"/>
+      <c r="B4" s="90" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="91"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="91"/>
+      <c r="K4" s="92"/>
     </row>
     <row r="5" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
@@ -1726,7 +1726,7 @@
         <f>SUM(K10:K13)</f>
         <v>35</v>
       </c>
-      <c r="M9" s="96">
+      <c r="M9" s="83">
         <f>K9-K11-K12</f>
         <v>34</v>
       </c>
@@ -1979,33 +1979,33 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="95" t="s">
+      <c r="A20" s="93" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="95"/>
-      <c r="C20" s="95"/>
-      <c r="D20" s="95"/>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="95"/>
+      <c r="B20" s="93"/>
+      <c r="C20" s="93"/>
+      <c r="D20" s="93"/>
+      <c r="E20" s="93"/>
+      <c r="F20" s="93"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="93"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="87" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="88"/>
-      <c r="D21" s="88"/>
-      <c r="E21" s="88"/>
-      <c r="F21" s="88"/>
-      <c r="G21" s="88"/>
-      <c r="H21" s="88"/>
-      <c r="I21" s="88"/>
-      <c r="J21" s="88"/>
-      <c r="K21" s="89"/>
+      <c r="B21" s="90" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="91"/>
+      <c r="D21" s="91"/>
+      <c r="E21" s="91"/>
+      <c r="F21" s="91"/>
+      <c r="G21" s="91"/>
+      <c r="H21" s="91"/>
+      <c r="I21" s="91"/>
+      <c r="J21" s="91"/>
+      <c r="K21" s="92"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
@@ -2887,16 +2887,16 @@
       <c r="K49" s="17"/>
     </row>
     <row r="50" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="95" t="s">
+      <c r="A50" s="93" t="s">
         <v>39</v>
       </c>
-      <c r="B50" s="95"/>
-      <c r="C50" s="95"/>
-      <c r="D50" s="95"/>
-      <c r="E50" s="95"/>
-      <c r="F50" s="95"/>
-      <c r="G50" s="95"/>
-      <c r="H50" s="95"/>
+      <c r="B50" s="93"/>
+      <c r="C50" s="93"/>
+      <c r="D50" s="93"/>
+      <c r="E50" s="93"/>
+      <c r="F50" s="93"/>
+      <c r="G50" s="93"/>
+      <c r="H50" s="93"/>
     </row>
     <row r="51" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
@@ -3006,68 +3006,68 @@
       <c r="J54" s="37"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="91" t="s">
+      <c r="A55" s="86" t="s">
         <v>40</v>
       </c>
-      <c r="B55" s="91"/>
-      <c r="C55" s="91"/>
-      <c r="D55" s="91"/>
-      <c r="E55" s="91"/>
-      <c r="F55" s="91"/>
-      <c r="G55" s="91"/>
-      <c r="H55" s="91"/>
-      <c r="I55" s="91"/>
+      <c r="B55" s="86"/>
+      <c r="C55" s="86"/>
+      <c r="D55" s="86"/>
+      <c r="E55" s="86"/>
+      <c r="F55" s="86"/>
+      <c r="G55" s="86"/>
+      <c r="H55" s="86"/>
+      <c r="I55" s="86"/>
     </row>
     <row r="56" spans="1:11" ht="32.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="84" t="s">
+      <c r="A56" s="94" t="s">
         <v>14</v>
       </c>
-      <c r="B56" s="84" t="s">
+      <c r="B56" s="94" t="s">
         <v>15</v>
       </c>
-      <c r="C56" s="84"/>
-      <c r="D56" s="84"/>
-      <c r="E56" s="84"/>
-      <c r="F56" s="84" t="s">
+      <c r="C56" s="94"/>
+      <c r="D56" s="94"/>
+      <c r="E56" s="94"/>
+      <c r="F56" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="G56" s="84"/>
+      <c r="G56" s="94"/>
       <c r="H56" s="38"/>
       <c r="I56" s="38"/>
     </row>
     <row r="57" spans="1:11" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="84"/>
-      <c r="B57" s="83" t="s">
+      <c r="A57" s="94"/>
+      <c r="B57" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="C57" s="84" t="s">
+      <c r="C57" s="94" t="s">
         <v>68</v>
       </c>
-      <c r="D57" s="84"/>
-      <c r="E57" s="83" t="s">
+      <c r="D57" s="94"/>
+      <c r="E57" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="F57" s="84" t="s">
+      <c r="F57" s="94" t="s">
         <v>57</v>
       </c>
-      <c r="G57" s="84" t="s">
+      <c r="G57" s="94" t="s">
         <v>19</v>
       </c>
       <c r="H57" s="38"/>
       <c r="I57" s="38"/>
     </row>
     <row r="58" spans="1:11" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="84"/>
-      <c r="B58" s="83"/>
+      <c r="A58" s="94"/>
+      <c r="B58" s="95"/>
       <c r="C58" s="53" t="s">
         <v>20</v>
       </c>
       <c r="D58" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="E58" s="83"/>
-      <c r="F58" s="84"/>
-      <c r="G58" s="84"/>
+      <c r="E58" s="95"/>
+      <c r="F58" s="94"/>
+      <c r="G58" s="94"/>
       <c r="H58" s="38"/>
       <c r="I58" s="38"/>
     </row>
@@ -3123,18 +3123,18 @@
         <v>5</v>
       </c>
       <c r="D61" s="36">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E61" s="35">
         <f>K8/K14*D61</f>
-        <v>11.590909090909092</v>
+        <v>17.386363636363637</v>
       </c>
       <c r="F61" s="35">
-        <v>20202.954545454548</v>
+        <v>30304.43181818182</v>
       </c>
       <c r="G61" s="35">
         <f>F61*E52</f>
-        <v>144126.00000000003</v>
+        <v>216189.00000000003</v>
       </c>
       <c r="H61" s="39"/>
       <c r="I61" s="39"/>
@@ -3150,18 +3150,18 @@
       </c>
       <c r="D62" s="45">
         <f>SUM(D60:D61)</f>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E62" s="45">
         <f>K8/K14*D62</f>
-        <v>18.545454545454547</v>
+        <v>24.340909090909093</v>
       </c>
       <c r="F62" s="45">
-        <v>32324.727272727276</v>
+        <v>42426.204545454551</v>
       </c>
       <c r="G62" s="45">
         <f>G60+G61</f>
-        <v>265460.56363636366</v>
+        <v>337523.56363636366</v>
       </c>
       <c r="H62" s="39"/>
       <c r="I62" s="39"/>
@@ -3369,19 +3369,19 @@
       </c>
       <c r="D71" s="49">
         <f>D62+D66+D70</f>
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E71" s="49">
         <f>E62+E66+E70</f>
-        <v>32.454545454545453</v>
+        <v>38.25</v>
       </c>
       <c r="F71" s="49">
         <f>F62+F66+F70</f>
-        <v>56568.272727272728</v>
+        <v>66669.75</v>
       </c>
       <c r="G71" s="49">
         <f>G62+G66+G70</f>
-        <v>393943.00909090909</v>
+        <v>466006.00909090909</v>
       </c>
       <c r="H71" s="39"/>
       <c r="I71" s="39"/>
@@ -3391,27 +3391,27 @@
       <c r="I72" s="41"/>
     </row>
     <row r="73" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="90" t="s">
+      <c r="A73" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="B73" s="90"/>
-      <c r="C73" s="90"/>
-      <c r="D73" s="90"/>
+      <c r="B73" s="85"/>
+      <c r="C73" s="85"/>
+      <c r="D73" s="85"/>
     </row>
     <row r="74" spans="1:9" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="84" t="s">
+      <c r="A74" s="94" t="s">
         <v>60</v>
       </c>
-      <c r="B74" s="87" t="s">
+      <c r="B74" s="90" t="s">
         <v>28</v>
       </c>
-      <c r="C74" s="88"/>
-      <c r="D74" s="89"/>
+      <c r="C74" s="91"/>
+      <c r="D74" s="92"/>
       <c r="E74" s="29"/>
       <c r="F74" s="29"/>
     </row>
     <row r="75" spans="1:9" ht="48.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="84"/>
+      <c r="A75" s="94"/>
       <c r="B75" s="5" t="s">
         <v>59</v>
       </c>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="B76" s="10">
         <f>G62</f>
-        <v>265460.56363636366</v>
+        <v>337523.56363636366</v>
       </c>
       <c r="C76" s="10">
         <f>G66</f>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="B77" s="10" cm="1">
         <f t="array" ref="B77:D77">B76:D76*0.6</f>
-        <v>159276.3381818182</v>
+        <v>202514.13818181818</v>
       </c>
       <c r="C77" s="10">
         <v>45763.969090909093</v>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="B78" s="10" cm="1">
         <f t="array" ref="B78:D78">B76:D76/3*0.2</f>
-        <v>17697.370909090911</v>
+        <v>22501.570909090911</v>
       </c>
       <c r="C78" s="10">
         <v>5084.885454545456</v>
@@ -3473,8 +3473,8 @@
       <c r="D78" s="10">
         <v>3480.6109090909094</v>
       </c>
-      <c r="E78" s="85"/>
-      <c r="F78" s="86"/>
+      <c r="E78" s="96"/>
+      <c r="F78" s="97"/>
     </row>
     <row r="79" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="B79" s="10" cm="1">
         <f t="array" ref="B79:D79">(B76:D76/3)*0.4</f>
-        <v>35394.741818181821</v>
+        <v>45003.141818181823</v>
       </c>
       <c r="C79" s="10">
         <v>10169.770909090912</v>
@@ -3490,8 +3490,8 @@
       <c r="D79" s="10">
         <v>6961.2218181818189</v>
       </c>
-      <c r="E79" s="85"/>
-      <c r="F79" s="86"/>
+      <c r="E79" s="96"/>
+      <c r="F79" s="97"/>
     </row>
     <row r="80" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="B80" s="58">
         <f>SUM(B76:B79)</f>
-        <v>477829.01454545459</v>
+        <v>607542.41454545467</v>
       </c>
       <c r="C80" s="58">
         <f>SUM(C76:C79)</f>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="B82" s="58" cm="1">
         <f t="array" ref="B82:D82">B80:D80*B81:D81/100</f>
-        <v>73846.302247933883</v>
+        <v>93892.918611570261</v>
       </c>
       <c r="C82" s="58">
         <v>21217.840214876036</v>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="B83" s="77">
         <f>B80+B82</f>
-        <v>551675.31679338845</v>
+        <v>701435.33315702493</v>
       </c>
       <c r="C83" s="77">
         <f>C80+C82</f>
@@ -3568,37 +3568,37 @@
       <c r="F83" s="29"/>
     </row>
     <row r="85" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A85" s="91" t="s">
+      <c r="A85" s="86" t="s">
         <v>62</v>
       </c>
-      <c r="B85" s="91"/>
-      <c r="C85" s="91"/>
-      <c r="D85" s="91"/>
-      <c r="E85" s="91"/>
-      <c r="F85" s="91"/>
-      <c r="G85" s="91"/>
+      <c r="B85" s="86"/>
+      <c r="C85" s="86"/>
+      <c r="D85" s="86"/>
+      <c r="E85" s="86"/>
+      <c r="F85" s="86"/>
+      <c r="G85" s="86"/>
     </row>
     <row r="86" spans="1:7" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B86" s="83" t="s">
+      <c r="B86" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="C86" s="84" t="s">
+      <c r="C86" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="D86" s="87" t="s">
+      <c r="D86" s="90" t="s">
         <v>28</v>
       </c>
-      <c r="E86" s="88"/>
-      <c r="F86" s="88"/>
-      <c r="G86" s="89"/>
+      <c r="E86" s="91"/>
+      <c r="F86" s="91"/>
+      <c r="G86" s="92"/>
     </row>
     <row r="87" spans="1:7" ht="53.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
-      <c r="B87" s="83"/>
-      <c r="C87" s="84"/>
+      <c r="B87" s="95"/>
+      <c r="C87" s="94"/>
       <c r="D87" s="7" t="s">
         <v>63</v>
       </c>
@@ -3695,7 +3695,7 @@
         <f>SUM(B88:B90)</f>
         <v>5</v>
       </c>
-      <c r="C91" s="97">
+      <c r="C91" s="84">
         <f>SUM(C88:C90)</f>
         <v>8155</v>
       </c>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="B95" s="64">
         <f>G91+G71</f>
-        <v>646712.1</v>
+        <v>718775.1</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -3744,41 +3744,63 @@
       </c>
       <c r="B96" s="64">
         <f>E71+B91</f>
-        <v>37.454545454545453</v>
+        <v>43.25</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="B97" s="65"/>
+      <c r="B97" s="65">
+        <f>B95/B96</f>
+        <v>16619.077456647399</v>
+      </c>
     </row>
     <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="B98" s="65"/>
+      <c r="B98" s="65">
+        <f>B97/12</f>
+        <v>1384.9231213872833</v>
+      </c>
     </row>
     <row r="99" spans="1:2" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="B99" s="65"/>
+      <c r="B99" s="65">
+        <f>K26/E71</f>
+        <v>386.66666666666669</v>
+      </c>
     </row>
     <row r="100" spans="1:2" ht="29.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="63" t="s">
         <v>109</v>
       </c>
-      <c r="B100" s="65"/>
+      <c r="B100" s="65">
+        <f>B101*8</f>
+        <v>1.7747179192962326</v>
+      </c>
     </row>
     <row r="101" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A101" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="B101" s="65"/>
+      <c r="B101" s="65">
+        <f>B99/K17</f>
+        <v>0.22183973991202907</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="E78:E79"/>
+    <mergeCell ref="F78:F79"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="D86:G86"/>
+    <mergeCell ref="B74:D74"/>
     <mergeCell ref="A73:D73"/>
     <mergeCell ref="A85:G85"/>
     <mergeCell ref="A3:K3"/>
@@ -3795,13 +3817,6 @@
     <mergeCell ref="E57:E58"/>
     <mergeCell ref="F57:F58"/>
     <mergeCell ref="G57:G58"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="E78:E79"/>
-    <mergeCell ref="F78:F79"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="D86:G86"/>
-    <mergeCell ref="B74:D74"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
